--- a/artfynd/A 30881-2025 artfynd.xlsx
+++ b/artfynd/A 30881-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111180852</v>
+        <v>111181142</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541346.7926165992</v>
+        <v>541358</v>
       </c>
       <c r="R2" t="n">
-        <v>6963370.219613944</v>
+        <v>6963466</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111181142</v>
+        <v>111181113</v>
       </c>
       <c r="B3" t="n">
-        <v>89590</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541358.4223123443</v>
+        <v>541358</v>
       </c>
       <c r="R3" t="n">
-        <v>6963465.536817129</v>
+        <v>6963466</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +874,7 @@
         <v>111180900</v>
       </c>
       <c r="B4" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541324.180861581</v>
+        <v>541324</v>
       </c>
       <c r="R4" t="n">
-        <v>6963419.351063898</v>
+        <v>6963419</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,12 +987,7 @@
         <v>111180783</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541356.2143780371</v>
+        <v>541356</v>
       </c>
       <c r="R5" t="n">
-        <v>6963349.748003015</v>
+        <v>6963349</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,37 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111181113</v>
+        <v>111180852</v>
       </c>
       <c r="B6" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541358.4223123443</v>
+        <v>541347</v>
       </c>
       <c r="R6" t="n">
-        <v>6963465.536817129</v>
+        <v>6963370</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30881-2025 artfynd.xlsx
+++ b/artfynd/A 30881-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111181142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111181113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111180900</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111180783</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111180852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>